--- a/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
+++ b/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Variables de monitoreo" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estimación por Requisitos'!$A$4:$Q$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estimación por Requisitos'!$A$4:$Q$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Requisitos Funcionales'!$A$1:$G$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Requisitos Técnicos'!$A$1:$F$53</definedName>
   </definedNames>
@@ -617,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -919,6 +919,15 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1179,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q187"/>
+  <dimension ref="A1:Q196"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1190,6 +1199,7 @@
     <col width="12" customWidth="1" min="6" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="15"/>
@@ -1269,6 +1279,11 @@
           <t>Capacidad agéntica</t>
         </is>
       </c>
+      <c r="K4" s="51" t="inlineStr">
+        <is>
+          <t>Entra en</t>
+        </is>
+      </c>
       <c r="L4" s="52" t="inlineStr">
         <is>
           <t>Talla</t>
@@ -1329,6 +1344,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L5" s="56" t="inlineStr">
         <is>
           <t>S</t>
@@ -1386,6 +1406,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L6" s="56" t="inlineStr">
         <is>
           <t>M</t>
@@ -1445,6 +1470,11 @@
       <c r="J7" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
       <c r="L7" s="56" t="inlineStr">
@@ -1507,6 +1537,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L8" s="56" t="inlineStr">
         <is>
           <t>XL</t>
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="J9" s="53" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L9" s="91" t="inlineStr">
         <is>
           <t>🟨 Escala de referencia (no oficial para todas las tallas): M ≈ 5 días (medio sprint) y L ≈ 10 días (1 sprint) están tomados literalmente del Acta de Estimación de Costo y Releases (21-ago-2026). S (≈3 días) y XL (≈20 días, el doble de L, por la regla de coherencia de tallaje de Víctor Martínez) son un supuesto para completar la escala — ajústelos si el equipo define otro valor. 1 sprint = 10 días hábiles (estándar SuraHis).</t>
@@ -1648,6 +1688,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="57" t="inlineStr">
@@ -1693,6 +1738,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="53" t="inlineStr">
@@ -1738,6 +1788,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L13" s="90" t="inlineStr">
         <is>
           <t>Referencia de Épicas (usada por la columna "¿En MVP?")</t>
@@ -1788,6 +1843,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L14" s="52" t="inlineStr">
         <is>
           <t>Épica / Gestor-Frente</t>
@@ -1867,17 +1927,22 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L15" s="58" t="inlineStr">
         <is>
           <t>Gestor de Monitoreo (Torre de Control)</t>
         </is>
       </c>
       <c r="M15" s="58">
-        <f>COUNTIFS($C$5:$C$187,L15,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L15,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N15" s="58">
-        <f>COUNTIFS($C$5:$C$187,L15,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L15,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O15" s="58" t="inlineStr">
@@ -1940,17 +2005,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L16" s="58" t="inlineStr">
         <is>
           <t>Interoperabilidad (Prestadores)</t>
         </is>
       </c>
       <c r="M16" s="58">
-        <f>COUNTIFS($C$5:$C$187,L16,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L16,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N16" s="58">
-        <f>COUNTIFS($C$5:$C$187,L16,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L16,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O16" s="58" t="inlineStr">
@@ -2013,17 +2083,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L17" s="60" t="inlineStr">
         <is>
           <t>Gestor de Evaluación</t>
         </is>
       </c>
       <c r="M17" s="60">
-        <f>COUNTIFS($C$5:$C$187,L17,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L17,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N17" s="60">
-        <f>COUNTIFS($C$5:$C$187,L17,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L17,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O17" s="60" t="inlineStr">
@@ -2086,17 +2161,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L18" s="60" t="inlineStr">
         <is>
           <t>Gestor de Solicitud</t>
         </is>
       </c>
       <c r="M18" s="60">
-        <f>COUNTIFS($C$5:$C$187,L18,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L18,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N18" s="60">
-        <f>COUNTIFS($C$5:$C$187,L18,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L18,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O18" s="60" t="inlineStr">
@@ -2159,32 +2239,37 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L19" s="62" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
       <c r="M19" s="62">
-        <f>COUNTIFS($C$5:$C$187,L19,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L19,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N19" s="62">
-        <f>COUNTIFS($C$5:$C$187,L19,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L19,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O19" s="62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P19" s="62" t="inlineStr">
         <is>
-          <t>No aplica (absorbido por Core)</t>
+          <t>Release 3 (dentro del MVP)</t>
         </is>
       </c>
       <c r="Q19" s="57" t="inlineStr">
         <is>
-          <t>Decidido el 03-ago-2026 (con Viviana Monsalve): NO se implementa como gestor agéntico independiente. La asignación de prestador queda encapsulada en SuraHis (Core), principio KISS.</t>
+          <t>Se retoma en v2 como gestor propio, revirtiendo la decisión del 03-ago-2026 que lo dejaba encapsulado en SuraHis. Entra solo su nivel 1 determinístico: reglas duras, ranking de red y bandeja human in the loop. El asistente explicativo con modelo y el componente conversacional (RF-075, RT-023) quedan fuera.</t>
         </is>
       </c>
     </row>
@@ -2230,11 +2315,11 @@
         </is>
       </c>
       <c r="M20" s="60">
-        <f>COUNTIFS($C$5:$C$187,L20,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L20,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N20" s="60">
-        <f>COUNTIFS($C$5:$C$187,L20,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L20,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O20" s="60" t="inlineStr">
@@ -2295,11 +2380,11 @@
         </is>
       </c>
       <c r="M21" s="60">
-        <f>COUNTIFS($C$5:$C$187,L21,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L21,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N21" s="60">
-        <f>COUNTIFS($C$5:$C$187,L21,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L21,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O21" s="60" t="inlineStr">
@@ -2358,17 +2443,22 @@
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L22" s="58" t="inlineStr">
         <is>
           <t>Gestor de Asignación</t>
         </is>
       </c>
       <c r="M22" s="58">
-        <f>COUNTIFS($C$5:$C$187,L22,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L22,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N22" s="58">
-        <f>COUNTIFS($C$5:$C$187,L22,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L22,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O22" s="58" t="inlineStr">
@@ -2429,11 +2519,11 @@
         </is>
       </c>
       <c r="M23" s="60">
-        <f>COUNTIFS($C$5:$C$187,L23,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L23,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N23" s="60">
-        <f>COUNTIFS($C$5:$C$187,L23,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L23,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O23" s="60" t="inlineStr">
@@ -2496,17 +2586,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L24" s="62" t="inlineStr">
         <is>
           <t>NEXO (Asesores)</t>
         </is>
       </c>
       <c r="M24" s="62">
-        <f>COUNTIFS($C$5:$C$187,L24,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L24,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N24" s="62">
-        <f>COUNTIFS($C$5:$C$187,L24,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L24,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O24" s="62" t="inlineStr">
@@ -2571,17 +2666,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L25" s="62" t="inlineStr">
         <is>
           <t>Gestor de Prestación</t>
         </is>
       </c>
       <c r="M25" s="62">
-        <f>COUNTIFS($C$5:$C$187,L25,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L25,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N25" s="62">
-        <f>COUNTIFS($C$5:$C$187,L25,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L25,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O25" s="62" t="inlineStr">
@@ -2648,17 +2748,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L26" s="62" t="inlineStr">
         <is>
           <t>AVA (Asesores — AVA)</t>
         </is>
       </c>
       <c r="M26" s="62">
-        <f>COUNTIFS($C$5:$C$187,L26,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L26,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N26" s="62">
-        <f>COUNTIFS($C$5:$C$187,L26,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L26,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O26" s="62" t="inlineStr">
@@ -2721,17 +2826,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L27" s="60" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
       <c r="M27" s="60">
-        <f>COUNTIFS($C$5:$C$187,L27,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L27,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N27" s="60">
-        <f>COUNTIFS($C$5:$C$187,L27,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L27,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O27" s="60" t="inlineStr">
@@ -2794,17 +2904,22 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L28" s="62" t="inlineStr">
         <is>
           <t>Gestor de Finalización</t>
         </is>
       </c>
       <c r="M28" s="62">
-        <f>COUNTIFS($C$5:$C$187,L28,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L28,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N28" s="62">
-        <f>COUNTIFS($C$5:$C$187,L28,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L28,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O28" s="62" t="inlineStr">
@@ -2867,17 +2982,22 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L29" s="62" t="inlineStr">
         <is>
           <t>Surahis</t>
         </is>
       </c>
       <c r="M29" s="62">
-        <f>COUNTIFS($C$5:$C$187,L29,$B$5:$B$187,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$196,L29,$B$5:$B$196,"Funcional")</f>
         <v/>
       </c>
       <c r="N29" s="62">
-        <f>COUNTIFS($C$5:$C$187,L29,$B$5:$B$187,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$196,L29,$B$5:$B$196,"Técnico")</f>
         <v/>
       </c>
       <c r="O29" s="62" t="inlineStr">
@@ -2940,6 +3060,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -2983,6 +3108,11 @@
       <c r="J31" s="53" t="inlineStr">
         <is>
           <t>Agéntica</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
       <c r="L31" s="115" t="n"/>
@@ -3036,6 +3166,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L32" s="108" t="inlineStr">
         <is>
           <t>Leyenda y criterio de esta estimación (Tech and Solve)</t>
@@ -3091,6 +3226,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L33" s="116" t="inlineStr">
         <is>
           <t>Fila adicionada</t>
@@ -3098,7 +3238,7 @@
       </c>
       <c r="M33" s="110" t="inlineStr">
         <is>
-          <t>Requisito funcional nuevo, RF-109 a RF-129. Elementos que el dibujo del MVP y la vista de tecnología exigen y que la hoja no tenía.</t>
+          <t>Requisito funcional o técnico nuevo. En v1, RF-109 a RF-129, por el dibujo del MVP y la vista de tecnología. En v2, RF-135 a RF-139 y RT-055 a RT-058, por lo que la banda del Gestor de Coordinación exige y la hoja no tenía.</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3285,7 @@
       </c>
       <c r="M34" s="110" t="inlineStr">
         <is>
-          <t>Requisito que no se pudo estimar. La duda concreta queda escrita en Observaciones. Son 11.</t>
+          <t>Requisito que no se pudo estimar. La duda concreta queda escrita en Observaciones. Son 14: 11 de v1 y 3 que aparecen al abrir Coordinación.</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3332,7 @@
       </c>
       <c r="M35" s="110" t="inlineStr">
         <is>
-          <t>Requisito que entra al MVP con una salvedad sobre qué cubre la talla, o cuya duda ya se cerró con una decisión del equipo; en ambos casos queda escrita en Observaciones. Son 9.</t>
+          <t>Requisito que entra al MVP con una salvedad sobre qué cubre la talla, o cuya duda ya se cerró con una decisión del equipo; en ambos casos queda escrita en Observaciones. Son 11.</t>
         </is>
       </c>
     </row>
@@ -3326,8 +3466,16 @@
       </c>
       <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
-      <c r="L38" s="115" t="n"/>
-      <c r="M38" s="115" t="n"/>
+      <c r="L38" s="120" t="inlineStr">
+        <is>
+          <t>Columna «Entra en»</t>
+        </is>
+      </c>
+      <c r="M38" s="110" t="inlineStr">
+        <is>
+          <t>Filtro rápido de versión. «v1» son los requisitos que ya estaban dentro del alcance estimado; «v2» son los 18 del Gestor de Coordinación que entran ahora más los 3 que quedaron en alerta. Las filas fuera del MVP quedan en blanco. El color de fila conserva el significado que tenía en v1.</t>
+        </is>
+      </c>
       <c r="N38" s="115" t="n"/>
       <c r="O38" s="115" t="n"/>
       <c r="P38" s="115" t="n"/>
@@ -3423,7 +3571,7 @@
       </c>
       <c r="M40" s="110" t="inlineStr">
         <is>
-          <t>76 requisitos del MVP tallados: 525 días hábiles, 52 sprints de un frente, con la escala de la propia hoja. La suma va sin margen de incertidumbre. Reparto: Gestor de Evaluación 138 d · Gestor de Monitoreo 97 d · Gestor de Solicitud 84 d · Transversal (principios) 59 d · Siniestro Integral 52 d · Transversal 50 d · Canales / Front Externos 43 d · Interoperabilidad (Prestadores) 2 d.</t>
+          <t>94 requisitos del MVP tallados: 637 días hábiles, 64 sprints de un frente, con la escala de la propia hoja. La suma va sin margen de incertidumbre. Reparto: Gestor de Evaluación 138 d · Gestor de Coordinación 112 d · Gestor de Monitoreo (Torre de Control) 97 d · Gestor de Solicitud 84 d · Transversal / Principios generales 59 d · Siniestro Integral 52 d · Transversal 50 d · Canales / Front Externos 43 d · Interoperabilidad (Prestadores) 2 d.</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3639,11 @@
           <t xml:space="preserve">Si el asegurado sugiere un prestador y está en convenio para los servicios que se requieren se genera la autorización sin problema a ese prestador </t>
         </is>
       </c>
-      <c r="E42" s="54" t="n"/>
+      <c r="E42" s="54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F42" s="53">
         <f>IF($E42="",0,INDEX($M$5:$M$8,MATCH($E42,$L$5:$L$8,0)))</f>
         <v/>
@@ -3505,7 +3657,16 @@
         <v/>
       </c>
       <c r="I42" s="53" t="n"/>
-      <c r="J42" s="53" t="n"/>
+      <c r="J42" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L42" s="108" t="inlineStr">
         <is>
           <t>Criterio de alcance</t>
@@ -3544,7 +3705,11 @@
 2. Cuando el asegurado solicita una autorización y en el ordenamiento esta un proveedor que atiende diferente al sugerido por el asegurado, se debe dar prioridad al que sugiere el asegurado</t>
         </is>
       </c>
-      <c r="E43" s="54" t="n"/>
+      <c r="E43" s="54" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
       <c r="F43" s="53">
         <f>IF($E43="",0,INDEX($M$5:$M$8,MATCH($E43,$L$5:$L$8,0)))</f>
         <v/>
@@ -3558,7 +3723,16 @@
         <v/>
       </c>
       <c r="I43" s="53" t="n"/>
-      <c r="J43" s="53" t="n"/>
+      <c r="J43" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L43" s="120" t="inlineStr">
         <is>
           <t>Qué entra</t>
@@ -3566,46 +3740,63 @@
       </c>
       <c r="M43" s="110" t="inlineStr">
         <is>
-          <t>La pertenencia al MVP se decidió requisito por requisito contra «resumen-arquitectura-gestores — Arquitectura MVP» y «arquitectura-tecnologia», no contra la columna «¿En MVP?», que se deriva por épica y por eso marca «Sí» a épicas donde solo una parte entra. Entran Solicitud, Evaluación, Siniestro Integral, los canales que el MVP habilita, las capas 1 y 2 de la torre, el acceso al dato vía el core y los transversales del ciclo de mejora y del plano de control. Quedan fuera Coordinación, Prestación, Finalización, Asignación, Nexo, AVA, la interoperabilidad de autorizaciones y las capas 3, 4 y 5 de la torre.</t>
+          <t>La pertenencia al MVP se decidió requisito por requisito contra «resumen-arquitectura-gestores — Arquitectura MVP» y «arquitectura-tecnologia», no contra la columna «¿En MVP?», que se deriva por épica y por eso marca «Sí» a épicas donde solo una parte entra. Entran Solicitud, Evaluación, Coordinación en su nivel 1 determinístico, Siniestro Integral, los canales que el MVP habilita, las capas 1 y 2 de la torre, el acceso al dato vía el core y los transversales del ciclo de mejora y del plano de control. Quedan fuera Prestación, Finalización, Asignación, Nexo, AVA, la interoperabilidad de autorizaciones, las capas 3, 4 y 5 de la torre, y los niveles 2 y 3 de Coordinación.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="57" t="inlineStr">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>RF-040</t>
         </is>
       </c>
-      <c r="B44" s="57" t="inlineStr">
+      <c r="B44" s="105" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="C44" s="57" t="inlineStr">
+      <c r="C44" s="105" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D44" s="57" t="inlineStr">
+      <c r="D44" s="105" t="inlineStr">
         <is>
           <t>Criterios de priorización de prestadores: quejas (Medallia), satisfacción, disponibilidad de citas, "suficiencia de la red" y tarifa del prestador.</t>
         </is>
       </c>
-      <c r="E44" s="54" t="n"/>
-      <c r="F44" s="53">
+      <c r="E44" s="123" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F44" s="105">
         <f>IF($E44="",0,INDEX($M$5:$M$8,MATCH($E44,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G44" s="53">
+      <c r="G44" s="105">
         <f>IF($F44=0,0,$F44/10)</f>
         <v/>
       </c>
-      <c r="H44" s="53">
+      <c r="H44" s="105">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C44,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="53" t="n"/>
+      <c r="I44" s="105" t="inlineStr">
+        <is>
+          <t>La talla cubre el motor de ordenamiento y el consumo de los criterios que hoy son consultables. Las cinco fuentes —Medallia, satisfacción, agenda de citas, suficiencia de red y tarifa— tienen dueños distintos; habilitar las que no estén expuestas no está en esta talla y su plazo lo declara su dueño.</t>
+        </is>
+      </c>
+      <c r="J44" s="105" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K44" s="124" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L44" s="115" t="n"/>
       <c r="M44" s="115" t="n"/>
       <c r="N44" s="115" t="n"/>
@@ -3634,7 +3825,11 @@
           <t>Si el prestador elegido no tiene convenio vigente, se asigna automáticamente el mejor rankeado y se notifica al cliente.</t>
         </is>
       </c>
-      <c r="E45" s="54" t="n"/>
+      <c r="E45" s="54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F45" s="53">
         <f>IF($E45="",0,INDEX($M$5:$M$8,MATCH($E45,$L$5:$L$8,0)))</f>
         <v/>
@@ -3648,7 +3843,16 @@
         <v/>
       </c>
       <c r="I45" s="53" t="n"/>
-      <c r="J45" s="53" t="n"/>
+      <c r="J45" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L45" s="108" t="inlineStr">
         <is>
           <t>Tres cosas que conviene saber antes de leer el total</t>
@@ -3681,7 +3885,11 @@
           <t>Si no hay red contratada en la ciudad, se escala a Convenios (bandeja de convenios en SuraHis).</t>
         </is>
       </c>
-      <c r="E46" s="54" t="n"/>
+      <c r="E46" s="54" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F46" s="53">
         <f>IF($E46="",0,INDEX($M$5:$M$8,MATCH($E46,$L$5:$L$8,0)))</f>
         <v/>
@@ -3695,7 +3903,16 @@
         <v/>
       </c>
       <c r="I46" s="53" t="n"/>
-      <c r="J46" s="53" t="n"/>
+      <c r="J46" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L46" s="120" t="inlineStr">
         <is>
           <t>La escala se contradice</t>
@@ -3703,7 +3920,7 @@
       </c>
       <c r="M46" s="110" t="inlineStr">
         <is>
-          <t>La tabla de tallaje dice S = 2 días y la nota de al lado dice S ≈ 3 días. Se usó la tabla, porque es la que alimenta la fórmula de la columna F. Si el equipo confirma los 3 días, el total sube 15 días (hay 15 requisitos en S).</t>
+          <t>La tabla de tallaje dice S = 2 días y la nota de al lado dice S ≈ 3 días. Se usó la tabla, porque es la que alimenta la fórmula de la columna F. Si el equipo confirma los 3 días, el total sube 21 días (hay 21 requisitos en S).</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3945,11 @@
           <t>mapear automáticamente la autorización contra el convenio/tarifa para pagar más rápido y reducir glosas.</t>
         </is>
       </c>
-      <c r="E47" s="54" t="n"/>
+      <c r="E47" s="54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="F47" s="53">
         <f>IF($E47="",0,INDEX($M$5:$M$8,MATCH($E47,$L$5:$L$8,0)))</f>
         <v/>
@@ -3742,7 +3963,16 @@
         <v/>
       </c>
       <c r="I47" s="53" t="n"/>
-      <c r="J47" s="53" t="n"/>
+      <c r="J47" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
       <c r="L47" s="120" t="inlineStr">
         <is>
           <t>Funcionales y técnicos se suman</t>
@@ -3750,7 +3980,7 @@
       </c>
       <c r="M47" s="110" t="inlineStr">
         <is>
-          <t>La hoja talla por separado el requisito funcional y el técnico, y así se respetó. Hay pares que describen la misma capacidad —RF-021 con RT-018, RF-024 con RT-020, RF-025 con RT-021, RF-001 con RT-011, RF-011 con RT-017—. Si el equipo decide contarlos una sola vez, el total baja hasta 32 días.</t>
+          <t>La hoja talla por separado el requisito funcional y el técnico, y así se respetó. Hay pares que describen la misma capacidad —RF-021 con RT-018, RF-024 con RT-020, RF-025 con RT-021, RF-001 con RT-011, RF-011 con RT-017, y en Coordinación RF-039 con RT-022 y RF-040 con RT-056—. Si el equipo decide contarlos una sola vez, el total baja hasta 47 días.</t>
         </is>
       </c>
     </row>
@@ -3998,17 +4228,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L52" s="114" t="inlineStr">
         <is>
           <t>Agéntica</t>
         </is>
       </c>
       <c r="M52" s="121">
-        <f>COUNTIF($J$5:$J$187,$L52)</f>
+        <f>COUNTIF($J$5:$J$196,$L52)</f>
         <v/>
       </c>
       <c r="N52" s="121">
-        <f>SUMIF($J$5:$J$187,$L52,$F$5:$F$187)</f>
+        <f>SUMIF($J$5:$J$196,$L52,$F$5:$F$196)</f>
         <v/>
       </c>
       <c r="O52" s="121">
@@ -4063,11 +4298,11 @@
         </is>
       </c>
       <c r="M53" s="121">
-        <f>COUNTIF($J$5:$J$187,$L53)</f>
+        <f>COUNTIF($J$5:$J$196,$L53)</f>
         <v/>
       </c>
       <c r="N53" s="121">
-        <f>SUMIF($J$5:$J$187,$L53,$F$5:$F$187)</f>
+        <f>SUMIF($J$5:$J$196,$L53,$F$5:$F$196)</f>
         <v/>
       </c>
       <c r="O53" s="121">
@@ -4124,17 +4359,22 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
       <c r="L54" s="114" t="inlineStr">
         <is>
           <t>Determinística</t>
         </is>
       </c>
       <c r="M54" s="121">
-        <f>COUNTIF($J$5:$J$187,$L54)</f>
+        <f>COUNTIF($J$5:$J$196,$L54)</f>
         <v/>
       </c>
       <c r="N54" s="121">
-        <f>SUMIF($J$5:$J$187,$L54,$F$5:$F$187)</f>
+        <f>SUMIF($J$5:$J$196,$L54,$F$5:$F$196)</f>
         <v/>
       </c>
       <c r="O54" s="121">
@@ -4341,6 +4581,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="53" t="inlineStr">
@@ -4460,6 +4705,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="105" t="inlineStr">
@@ -4507,6 +4757,11 @@
       <c r="J62" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -4965,6 +5220,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="53" t="inlineStr">
@@ -5228,6 +5488,11 @@
         </is>
       </c>
       <c r="J81" s="53" t="n"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="57" t="inlineStr">
@@ -5569,6 +5834,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="53" t="inlineStr">
@@ -5988,6 +6258,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="57" t="inlineStr">
@@ -6249,41 +6524,50 @@
       <c r="J108" s="53" t="n"/>
     </row>
     <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="106" t="inlineStr">
         <is>
           <t>RF-105</t>
         </is>
       </c>
-      <c r="B109" s="53" t="inlineStr">
+      <c r="B109" s="106" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="C109" s="53" t="inlineStr">
+      <c r="C109" s="106" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D109" s="53" t="inlineStr">
+      <c r="D109" s="106" t="inlineStr">
         <is>
           <t>Registrar los requisitos funcionales de cara a la asignación de proveedor, cambio de proveedor y lo que la IA podrá interactuar con el cliente</t>
         </is>
       </c>
-      <c r="E109" s="54" t="n"/>
-      <c r="F109" s="53">
+      <c r="E109" s="107" t="n"/>
+      <c r="F109" s="106">
         <f>IF($E109="",0,INDEX($M$5:$M$8,MATCH($E109,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G109" s="53">
+      <c r="G109" s="106">
         <f>IF($F109=0,0,$F109/10)</f>
         <v/>
       </c>
-      <c r="H109" s="53">
+      <c r="H109" s="106">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C109,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I109" s="53" t="n"/>
-      <c r="J109" s="53" t="n"/>
+      <c r="I109" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No estimable como está redactado. Pide «registrar los requisitos funcionales» de la asignación y del cambio de proveedor, es decir es un requisito sobre el levantamiento y no sobre la construcción. La parte que sí es construible quedó tallada en RF-038, RF-039 y RF-139; la interacción de la IA con el cliente pertenece al nivel 2, fuera de este alcance.</t>
+        </is>
+      </c>
+      <c r="J109" s="106" t="n"/>
+      <c r="K109" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="57" t="inlineStr">
@@ -6440,6 +6724,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="57" t="inlineStr">
@@ -6483,6 +6772,11 @@
       <c r="J114" s="53" t="inlineStr">
         <is>
           <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -6526,6 +6820,11 @@
         </is>
       </c>
       <c r="J115" s="53" t="n"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="57" t="inlineStr">
@@ -6571,6 +6870,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="53" t="inlineStr">
@@ -6616,6 +6920,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="57" t="inlineStr">
@@ -6661,6 +6970,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="53" t="inlineStr">
@@ -6706,6 +7020,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="105" t="inlineStr">
@@ -6755,6 +7074,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="53" t="inlineStr">
@@ -6800,6 +7124,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="57" t="inlineStr">
@@ -6845,6 +7174,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="53" t="inlineStr">
@@ -6888,6 +7222,11 @@
       <c r="J123" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -6931,6 +7270,11 @@
         </is>
       </c>
       <c r="J124" s="53" t="n"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="53" t="inlineStr">
@@ -6974,6 +7318,11 @@
       <c r="J125" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -7058,6 +7407,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="106" t="inlineStr">
@@ -7099,6 +7453,11 @@
         </is>
       </c>
       <c r="J128" s="53" t="n"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="53" t="inlineStr">
@@ -7144,6 +7503,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="57" t="inlineStr">
@@ -7187,6 +7551,11 @@
       <c r="J130" s="53" t="inlineStr">
         <is>
           <t>Agéntica</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -7230,6 +7599,11 @@
         </is>
       </c>
       <c r="J131" s="53" t="n"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="57" t="inlineStr">
@@ -7275,6 +7649,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="53" t="inlineStr">
@@ -7320,6 +7699,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="57" t="inlineStr">
@@ -7342,7 +7726,11 @@
           <t>Arranca con motor 100% determinístico (reglas duras de elegibilidad, convenios, capacidad, ubicación y costo).</t>
         </is>
       </c>
-      <c r="E134" s="54" t="n"/>
+      <c r="E134" s="54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="F134" s="53">
         <f>IF($E134="",0,INDEX($M$5:$M$8,MATCH($E134,$L$5:$L$8,0)))</f>
         <v/>
@@ -7356,7 +7744,16 @@
         <v/>
       </c>
       <c r="I134" s="53" t="n"/>
-      <c r="J134" s="53" t="n"/>
+      <c r="J134" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="53" t="inlineStr">
@@ -7396,78 +7793,104 @@
       <c r="J135" s="53" t="n"/>
     </row>
     <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="57" t="inlineStr">
+      <c r="A136" s="105" t="inlineStr">
         <is>
           <t>RT-024</t>
         </is>
       </c>
-      <c r="B136" s="57" t="inlineStr">
+      <c r="B136" s="105" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="C136" s="57" t="inlineStr">
+      <c r="C136" s="105" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D136" s="57" t="inlineStr">
+      <c r="D136" s="105" t="inlineStr">
         <is>
           <t>Niveles de madurez agéntica: Nivel 1 determinístico → Nivel 2 + asistente explicativo → Nivel 3 agente autónomo (futuro, fuera de alcance actual).</t>
         </is>
       </c>
-      <c r="E136" s="54" t="n"/>
-      <c r="F136" s="53">
+      <c r="E136" s="123" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F136" s="105">
         <f>IF($E136="",0,INDEX($M$5:$M$8,MATCH($E136,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G136" s="53">
+      <c r="G136" s="105">
         <f>IF($F136=0,0,$F136/10)</f>
         <v/>
       </c>
-      <c r="H136" s="53">
+      <c r="H136" s="105">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C136,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I136" s="53" t="n"/>
-      <c r="J136" s="53" t="n"/>
+      <c r="I136" s="105" t="inlineStr">
+        <is>
+          <t>Entra solo como costura: el motor determinístico queda detrás de una interfaz para que el nivel 2 —asistente explicativo con modelo— no obligue a rehacerlo. El nivel 2 y el nivel 3 quedan fuera del MVP.</t>
+        </is>
+      </c>
+      <c r="J136" s="105" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K136" s="124" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="53" t="inlineStr">
+      <c r="A137" s="106" t="inlineStr">
         <is>
           <t>RT-025</t>
         </is>
       </c>
-      <c r="B137" s="53" t="inlineStr">
+      <c r="B137" s="106" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="C137" s="53" t="inlineStr">
+      <c r="C137" s="106" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D137" s="53" t="inlineStr">
+      <c r="D137" s="106" t="inlineStr">
         <is>
           <t>Integración con prestadores externos preferiblemente vía API con retroalimentación de estados.</t>
         </is>
       </c>
-      <c r="E137" s="54" t="n"/>
-      <c r="F137" s="53">
+      <c r="E137" s="107" t="n"/>
+      <c r="F137" s="106">
         <f>IF($E137="",0,INDEX($M$5:$M$8,MATCH($E137,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G137" s="53">
+      <c r="G137" s="106">
         <f>IF($F137=0,0,$F137/10)</f>
         <v/>
       </c>
-      <c r="H137" s="53">
+      <c r="H137" s="106">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C137,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I137" s="53" t="n"/>
-      <c r="J137" s="53" t="n"/>
+      <c r="I137" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No estimable: «preferiblemente vía API» no acota el alcance ni nombra los prestadores a integrar, y la retroalimentación de estados desde el prestador pertenece a la épica de Interoperabilidad, cuyo plazo declara su dueño.</t>
+        </is>
+      </c>
+      <c r="J137" s="106" t="n"/>
+      <c r="K137" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="57" t="inlineStr">
@@ -7490,7 +7913,11 @@
           <t>Bandeja "human in the loop" para casos donde ni las reglas ni la recomendación logran asignar un prestador.</t>
         </is>
       </c>
-      <c r="E138" s="54" t="n"/>
+      <c r="E138" s="54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F138" s="53">
         <f>IF($E138="",0,INDEX($M$5:$M$8,MATCH($E138,$L$5:$L$8,0)))</f>
         <v/>
@@ -7504,44 +7931,62 @@
         <v/>
       </c>
       <c r="I138" s="53" t="n"/>
-      <c r="J138" s="53" t="n"/>
+      <c r="J138" s="53" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="30" customHeight="1">
-      <c r="A139" s="53" t="inlineStr">
+      <c r="A139" s="106" t="inlineStr">
         <is>
           <t>RT-027</t>
         </is>
       </c>
-      <c r="B139" s="53" t="inlineStr">
+      <c r="B139" s="106" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="C139" s="53" t="inlineStr">
+      <c r="C139" s="106" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D139" s="53" t="inlineStr">
+      <c r="D139" s="106" t="inlineStr">
         <is>
           <t>Es uno de los gestores menos profundizados técnicamente a la fecha — "no se ha hecho zoom" todavía.</t>
         </is>
       </c>
-      <c r="E139" s="54" t="n"/>
-      <c r="F139" s="53">
+      <c r="E139" s="107" t="n"/>
+      <c r="F139" s="106">
         <f>IF($E139="",0,INDEX($M$5:$M$8,MATCH($E139,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G139" s="53">
+      <c r="G139" s="106">
         <f>IF($F139=0,0,$F139/10)</f>
         <v/>
       </c>
-      <c r="H139" s="53">
+      <c r="H139" s="106">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C139,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I139" s="53" t="n"/>
-      <c r="J139" s="53" t="n"/>
+      <c r="I139" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No es un requisito sino la observación de que el gestor es el menos profundizado técnicamente. Es el riesgo principal de esta estimación y se declara como tal: la talla se construyó desde el dibujo y desde las reglas escritas, no desde un diseño detallado.</t>
+        </is>
+      </c>
+      <c r="J139" s="106" t="n"/>
+      <c r="K139" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="57" t="inlineStr">
@@ -7661,6 +8106,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="53" t="inlineStr">
@@ -7704,6 +8154,11 @@
       <c r="J143" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -7932,6 +8387,11 @@
         </is>
       </c>
       <c r="J149" s="53" t="n"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="106" t="inlineStr">
@@ -7973,6 +8433,11 @@
         </is>
       </c>
       <c r="J150" s="53" t="n"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="53" t="inlineStr">
@@ -8162,6 +8627,11 @@
         </is>
       </c>
       <c r="J155" s="53" t="n"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="57" t="inlineStr">
@@ -8207,6 +8677,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="105" t="inlineStr">
@@ -8254,6 +8729,11 @@
       <c r="J157" s="53" t="inlineStr">
         <is>
           <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -8449,6 +8929,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="106" t="inlineStr">
@@ -8490,6 +8975,11 @@
         </is>
       </c>
       <c r="J163" s="53" t="n"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="57" t="inlineStr">
@@ -8535,6 +9025,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="53" t="inlineStr">
@@ -8580,6 +9075,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="57" t="inlineStr">
@@ -8625,6 +9125,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="98" t="inlineStr">
@@ -8670,6 +9175,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="98" t="inlineStr">
@@ -8715,6 +9225,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="98" t="inlineStr">
@@ -8760,6 +9275,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="98" t="inlineStr">
@@ -8805,6 +9325,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="98" t="inlineStr">
@@ -8850,6 +9375,11 @@
           <t>Agéntica</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="98" t="inlineStr">
@@ -8895,6 +9425,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="98" t="inlineStr">
@@ -8940,6 +9475,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="98" t="inlineStr">
@@ -8985,6 +9525,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="98" t="inlineStr">
@@ -9030,6 +9575,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="98" t="inlineStr">
@@ -9075,6 +9625,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="98" t="inlineStr">
@@ -9120,6 +9675,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="98" t="inlineStr">
@@ -9165,6 +9725,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="98" t="inlineStr">
@@ -9210,6 +9775,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="98" t="inlineStr">
@@ -9255,6 +9825,11 @@
           <t>Determinística</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="98" t="inlineStr">
@@ -9300,6 +9875,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="98" t="inlineStr">
@@ -9345,6 +9925,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="98" t="inlineStr">
@@ -9390,6 +9975,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="98" t="inlineStr">
@@ -9435,6 +10025,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="98" t="inlineStr">
@@ -9480,6 +10075,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="98" t="inlineStr">
@@ -9525,6 +10125,11 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="98" t="inlineStr">
@@ -9570,9 +10175,464 @@
           <t>Habilitadora</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="98" t="inlineStr">
+        <is>
+          <t>RF-135</t>
+        </is>
+      </c>
+      <c r="B188" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C188" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D188" s="98" t="inlineStr">
+        <is>
+          <t>Api orquestadora del Gestor de Coordinación: punto único de entrada por tipo de solicitud, con el mismo rol de orquestador que los otros dos gestores.</t>
+        </is>
+      </c>
+      <c r="E188" s="126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F188" s="98">
+        <f>IF($E188="",0,INDEX($M$5:$M$8,MATCH($E188,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G188" s="98">
+        <f>IF($F188=0,0,$F188/10)</f>
+        <v/>
+      </c>
+      <c r="H188" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C188,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I188" s="98" t="n"/>
+      <c r="J188" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K188" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="98" t="inlineStr">
+        <is>
+          <t>RF-136</t>
+        </is>
+      </c>
+      <c r="B189" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C189" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D189" s="98" t="inlineStr">
+        <is>
+          <t>Traza de la decisión de asignación: prestador elegido, criterio aplicado, candidatos descartados y peso de cada criterio en el momento de decidir.</t>
+        </is>
+      </c>
+      <c r="E189" s="126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F189" s="98">
+        <f>IF($E189="",0,INDEX($M$5:$M$8,MATCH($E189,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G189" s="98">
+        <f>IF($F189=0,0,$F189/10)</f>
+        <v/>
+      </c>
+      <c r="H189" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C189,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I189" s="98" t="n"/>
+      <c r="J189" s="98" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K189" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="98" t="inlineStr">
+        <is>
+          <t>RF-137</t>
+        </is>
+      </c>
+      <c r="B190" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C190" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D190" s="98" t="inlineStr">
+        <is>
+          <t>Publica al bus el evento de prestador asignado, con la llave de correlación del caso y del siniestro padre, para que la torre lo lea.</t>
+        </is>
+      </c>
+      <c r="E190" s="126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F190" s="98">
+        <f>IF($E190="",0,INDEX($M$5:$M$8,MATCH($E190,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G190" s="98">
+        <f>IF($F190=0,0,$F190/10)</f>
+        <v/>
+      </c>
+      <c r="H190" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C190,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I190" s="98" t="n"/>
+      <c r="J190" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K190" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="98" t="inlineStr">
+        <is>
+          <t>RF-138</t>
+        </is>
+      </c>
+      <c r="B191" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C191" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D191" s="98" t="inlineStr">
+        <is>
+          <t>Notifica al cliente el prestador asignado y cualquier cambio posterior de prestador.</t>
+        </is>
+      </c>
+      <c r="E191" s="126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F191" s="98">
+        <f>IF($E191="",0,INDEX($M$5:$M$8,MATCH($E191,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G191" s="98">
+        <f>IF($F191=0,0,$F191/10)</f>
+        <v/>
+      </c>
+      <c r="H191" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C191,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I191" s="98" t="n"/>
+      <c r="J191" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K191" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="98" t="inlineStr">
+        <is>
+          <t>RF-139</t>
+        </is>
+      </c>
+      <c r="B192" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C192" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D192" s="98" t="inlineStr">
+        <is>
+          <t>Registra el cambio de prestador con su motivo, de modo que el caso conserve el histórico de asignaciones y no solo la última.</t>
+        </is>
+      </c>
+      <c r="E192" s="126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F192" s="98">
+        <f>IF($E192="",0,INDEX($M$5:$M$8,MATCH($E192,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G192" s="98">
+        <f>IF($F192=0,0,$F192/10)</f>
+        <v/>
+      </c>
+      <c r="H192" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C192,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I192" s="98" t="n"/>
+      <c r="J192" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K192" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="98" t="inlineStr">
+        <is>
+          <t>RT-055</t>
+        </is>
+      </c>
+      <c r="B193" s="98" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C193" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D193" s="98" t="inlineStr">
+        <is>
+          <t>Reglas de asignación versionadas con vigencia y autor, almacenadas fuera del código y expuestas como herramienta, no embebidas en lógica de aplicación.</t>
+        </is>
+      </c>
+      <c r="E193" s="126" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F193" s="98">
+        <f>IF($E193="",0,INDEX($M$5:$M$8,MATCH($E193,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G193" s="98">
+        <f>IF($F193=0,0,$F193/10)</f>
+        <v/>
+      </c>
+      <c r="H193" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C193,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I193" s="98" t="n"/>
+      <c r="J193" s="98" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K193" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="98" t="inlineStr">
+        <is>
+          <t>RT-056</t>
+        </is>
+      </c>
+      <c r="B194" s="98" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C194" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D194" s="98" t="inlineStr">
+        <is>
+          <t>Pesos del ranking como configuración y no como código, administrados por la API de gestión y configuraciones del plano de control.</t>
+        </is>
+      </c>
+      <c r="E194" s="126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F194" s="98">
+        <f>IF($E194="",0,INDEX($M$5:$M$8,MATCH($E194,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G194" s="98">
+        <f>IF($F194=0,0,$F194/10)</f>
+        <v/>
+      </c>
+      <c r="H194" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C194,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I194" s="98" t="n"/>
+      <c r="J194" s="98" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K194" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="98" t="inlineStr">
+        <is>
+          <t>RT-057</t>
+        </is>
+      </c>
+      <c r="B195" s="98" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C195" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D195" s="98" t="inlineStr">
+        <is>
+          <t>Lectura del catálogo de red, del convenio vigente y de la tarifa por Domain API de SuraHis sobre Apigee, expuesta como herramienta en APIM.</t>
+        </is>
+      </c>
+      <c r="E195" s="126" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F195" s="98">
+        <f>IF($E195="",0,INDEX($M$5:$M$8,MATCH($E195,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G195" s="98">
+        <f>IF($F195=0,0,$F195/10)</f>
+        <v/>
+      </c>
+      <c r="H195" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C195,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I195" s="98" t="n"/>
+      <c r="J195" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K195" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="98" t="inlineStr">
+        <is>
+          <t>RT-058</t>
+        </is>
+      </c>
+      <c r="B196" s="98" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C196" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D196" s="98" t="inlineStr">
+        <is>
+          <t>Namespace propio del gestor en AKS, con imagen en Azure Container Registry, identidad técnica y secretos en Key Vault.</t>
+        </is>
+      </c>
+      <c r="E196" s="126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F196" s="98">
+        <f>IF($E196="",0,INDEX($M$5:$M$8,MATCH($E196,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G196" s="98">
+        <f>IF($F196=0,0,$F196/10)</f>
+        <v/>
+      </c>
+      <c r="H196" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C196,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I196" s="98" t="n"/>
+      <c r="J196" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K196" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q187"/>
+  <autoFilter ref="A4:Q196"/>
   <mergeCells count="16">
     <mergeCell ref="M48:Q48"/>
     <mergeCell ref="M40:Q40"/>
@@ -9591,12 +10651,15 @@
     <mergeCell ref="M36:Q36"/>
     <mergeCell ref="L3:N3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E5:E187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="E5:E196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$L$5:$L$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Agéntica,Habilitadora,Determinística"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K5:K196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"v1,v2"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
+++ b/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O19" s="62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="P19" s="62" t="inlineStr">

--- a/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
+++ b/SURA/gestores-sura/estimacin mvp/v2/2 Gestores_Seguimiento_Requerimientos_2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Variables de monitoreo" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estimación por Requisitos'!$A$4:$Q$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estimación por Requisitos'!$A$4:$Q$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Requisitos Funcionales'!$A$1:$G$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Requisitos Técnicos'!$A$1:$F$53</definedName>
   </definedNames>
@@ -1188,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q196"/>
+  <dimension ref="A1:Q203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1938,11 +1938,11 @@
         </is>
       </c>
       <c r="M15" s="58">
-        <f>COUNTIFS($C$5:$C$196,L15,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L15,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N15" s="58">
-        <f>COUNTIFS($C$5:$C$196,L15,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L15,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O15" s="58" t="inlineStr">
@@ -2016,11 +2016,11 @@
         </is>
       </c>
       <c r="M16" s="58">
-        <f>COUNTIFS($C$5:$C$196,L16,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L16,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N16" s="58">
-        <f>COUNTIFS($C$5:$C$196,L16,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L16,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O16" s="58" t="inlineStr">
@@ -2094,11 +2094,11 @@
         </is>
       </c>
       <c r="M17" s="60">
-        <f>COUNTIFS($C$5:$C$196,L17,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L17,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N17" s="60">
-        <f>COUNTIFS($C$5:$C$196,L17,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L17,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O17" s="60" t="inlineStr">
@@ -2172,11 +2172,11 @@
         </is>
       </c>
       <c r="M18" s="60">
-        <f>COUNTIFS($C$5:$C$196,L18,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L18,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N18" s="60">
-        <f>COUNTIFS($C$5:$C$196,L18,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L18,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O18" s="60" t="inlineStr">
@@ -2250,11 +2250,11 @@
         </is>
       </c>
       <c r="M19" s="62">
-        <f>COUNTIFS($C$5:$C$196,L19,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L19,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N19" s="62">
-        <f>COUNTIFS($C$5:$C$196,L19,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L19,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O19" s="62" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Q19" s="57" t="inlineStr">
         <is>
-          <t>Se retoma en v2 como gestor propio, revirtiendo la decisión del 03-ago-2026 que lo dejaba encapsulado en SuraHis. Entra solo su nivel 1 determinístico: reglas duras, ranking de red y bandeja human in the loop. El asistente explicativo con modelo y el componente conversacional (RF-075, RT-023) quedan fuera.</t>
+          <t>Entra en el MVP solo su nivel 1 determinístico, sobre el diseño de la página «Arquitectura General de Gestores» de resumen-arquitectura-gestores: api orquestadora por tipo de solicitud, modelo experto Coordinador autorización, la decisión de proveedor sugerido con evaluar y sugerir como pasos, las dos bandejas y el golden set del coordinador. El asistente explicativo con modelo y el componente conversacional quedan fuera.</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="M20" s="60">
-        <f>COUNTIFS($C$5:$C$196,L20,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L20,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N20" s="60">
-        <f>COUNTIFS($C$5:$C$196,L20,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L20,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O20" s="60" t="inlineStr">
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="M21" s="60">
-        <f>COUNTIFS($C$5:$C$196,L21,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L21,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N21" s="60">
-        <f>COUNTIFS($C$5:$C$196,L21,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L21,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O21" s="60" t="inlineStr">
@@ -2454,11 +2454,11 @@
         </is>
       </c>
       <c r="M22" s="58">
-        <f>COUNTIFS($C$5:$C$196,L22,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L22,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N22" s="58">
-        <f>COUNTIFS($C$5:$C$196,L22,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L22,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O22" s="58" t="inlineStr">
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="M23" s="60">
-        <f>COUNTIFS($C$5:$C$196,L23,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L23,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N23" s="60">
-        <f>COUNTIFS($C$5:$C$196,L23,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L23,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O23" s="60" t="inlineStr">
@@ -2597,11 +2597,11 @@
         </is>
       </c>
       <c r="M24" s="62">
-        <f>COUNTIFS($C$5:$C$196,L24,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L24,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N24" s="62">
-        <f>COUNTIFS($C$5:$C$196,L24,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L24,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O24" s="62" t="inlineStr">
@@ -2677,11 +2677,11 @@
         </is>
       </c>
       <c r="M25" s="62">
-        <f>COUNTIFS($C$5:$C$196,L25,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L25,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N25" s="62">
-        <f>COUNTIFS($C$5:$C$196,L25,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L25,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O25" s="62" t="inlineStr">
@@ -2759,11 +2759,11 @@
         </is>
       </c>
       <c r="M26" s="62">
-        <f>COUNTIFS($C$5:$C$196,L26,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L26,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N26" s="62">
-        <f>COUNTIFS($C$5:$C$196,L26,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L26,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O26" s="62" t="inlineStr">
@@ -2837,11 +2837,11 @@
         </is>
       </c>
       <c r="M27" s="60">
-        <f>COUNTIFS($C$5:$C$196,L27,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L27,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N27" s="60">
-        <f>COUNTIFS($C$5:$C$196,L27,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L27,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O27" s="60" t="inlineStr">
@@ -2915,11 +2915,11 @@
         </is>
       </c>
       <c r="M28" s="62">
-        <f>COUNTIFS($C$5:$C$196,L28,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L28,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N28" s="62">
-        <f>COUNTIFS($C$5:$C$196,L28,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L28,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O28" s="62" t="inlineStr">
@@ -2993,11 +2993,11 @@
         </is>
       </c>
       <c r="M29" s="62">
-        <f>COUNTIFS($C$5:$C$196,L29,$B$5:$B$196,"Funcional")</f>
+        <f>COUNTIFS($C$5:$C$203,L29,$B$5:$B$203,"Funcional")</f>
         <v/>
       </c>
       <c r="N29" s="62">
-        <f>COUNTIFS($C$5:$C$196,L29,$B$5:$B$196,"Técnico")</f>
+        <f>COUNTIFS($C$5:$C$203,L29,$B$5:$B$203,"Técnico")</f>
         <v/>
       </c>
       <c r="O29" s="62" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="M33" s="110" t="inlineStr">
         <is>
-          <t>Requisito funcional o técnico nuevo. En v1, RF-109 a RF-129, por el dibujo del MVP y la vista de tecnología. En v2, RF-135 a RF-139 y RT-055 a RT-058, por lo que la banda del Gestor de Coordinación exige y la hoja no tenía.</t>
+          <t>Requisito funcional o técnico nuevo. En una primera pasada, RF-109 a RF-129, por el dibujo del MVP y la vista de tecnología. En esta, RF-135 a RF-142 y RT-055 a RT-059, por lo que el diseño del Gestor de Coordinación exige y la hoja no tenía.</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M34" s="110" t="inlineStr">
         <is>
-          <t>Requisito que no se pudo estimar. La duda concreta queda escrita en Observaciones. Son 14: 11 de v1 y 3 que aparecen al abrir Coordinación.</t>
+          <t>Requisito que no se pudo estimar. La duda concreta queda escrita en Observaciones. Son 17.</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="M35" s="110" t="inlineStr">
         <is>
-          <t>Requisito que entra al MVP con una salvedad sobre qué cubre la talla, o cuya duda ya se cerró con una decisión del equipo; en ambos casos queda escrita en Observaciones. Son 11.</t>
+          <t>Requisito que entra al MVP con una salvedad sobre qué cubre la talla, o cuya duda ya se cerró con una decisión del equipo; en ambos casos queda escrita en Observaciones. Son 12.</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="M40" s="110" t="inlineStr">
         <is>
-          <t>94 requisitos del MVP tallados: 637 días hábiles, 64 sprints de un frente, con la escala de la propia hoja. La suma va sin margen de incertidumbre. Reparto: Gestor de Evaluación 138 d · Gestor de Coordinación 112 d · Gestor de Monitoreo (Torre de Control) 97 d · Gestor de Solicitud 84 d · Transversal / Principios generales 59 d · Siniestro Integral 52 d · Transversal 50 d · Canales / Front Externos 43 d · Interoperabilidad (Prestadores) 2 d.</t>
+          <t>98 requisitos del MVP tallados: 659 días hábiles, 65.9 sprints de un frente, con la escala de la propia hoja. La suma va sin margen de incertidumbre. Reparto: Gestor de Evaluación 138 d · Gestor de Coordinación 134 d · Gestor de Monitoreo (Torre de Control) 97 d · Gestor de Solicitud 84 d · Transversal / Principios generales 59 d · Siniestro Integral 52 d · Transversal 50 d · Canales / Front Externos 43 d · Interoperabilidad (Prestadores) 2 d.</t>
         </is>
       </c>
     </row>
@@ -3865,50 +3865,54 @@
       <c r="Q45" s="115" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="57" t="inlineStr">
+      <c r="A46" s="105" t="inlineStr">
         <is>
           <t>RF-042</t>
         </is>
       </c>
-      <c r="B46" s="57" t="inlineStr">
+      <c r="B46" s="105" t="inlineStr">
         <is>
           <t>Funcional</t>
         </is>
       </c>
-      <c r="C46" s="57" t="inlineStr">
+      <c r="C46" s="105" t="inlineStr">
         <is>
           <t>Gestor de Coordinación</t>
         </is>
       </c>
-      <c r="D46" s="57" t="inlineStr">
+      <c r="D46" s="105" t="inlineStr">
         <is>
           <t>Si no hay red contratada en la ciudad, se escala a Convenios (bandeja de convenios en SuraHis).</t>
         </is>
       </c>
-      <c r="E46" s="54" t="inlineStr">
+      <c r="E46" s="123" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="105">
         <f>IF($E46="",0,INDEX($M$5:$M$8,MATCH($E46,$L$5:$L$8,0)))</f>
         <v/>
       </c>
-      <c r="G46" s="53">
+      <c r="G46" s="105">
         <f>IF($F46=0,0,$F46/10)</f>
         <v/>
       </c>
-      <c r="H46" s="53">
+      <c r="H46" s="105">
         <f>IFERROR(INDEX($O$15:$O$29,MATCH($C46,$L$15:$L$29,0)),"🟨 validar")</f>
         <v/>
       </c>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="53" t="inlineStr">
+      <c r="I46" s="105" t="inlineStr">
+        <is>
+          <t>🟨 Dos redacciones distintas en artefactos del proyecto: la hoja de estimación dice que se escala a la bandeja de convenios en SuraHis, y la hoja de seguimiento de la torre dice que se recomienda la ciudad más cercana. El diseño base resuelve «sin convenio» hacia la bandeja autorizaciones-convenios, y la talla cubre eso. Recomendar otra ciudad es una capacidad distinta y no está tallada.</t>
+        </is>
+      </c>
+      <c r="J46" s="105" t="inlineStr">
         <is>
           <t>Determinística</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="124" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
@@ -3920,7 +3924,7 @@
       </c>
       <c r="M46" s="110" t="inlineStr">
         <is>
-          <t>La tabla de tallaje dice S = 2 días y la nota de al lado dice S ≈ 3 días. Se usó la tabla, porque es la que alimenta la fórmula de la columna F. Si el equipo confirma los 3 días, el total sube 21 días (hay 21 requisitos en S).</t>
+          <t>La tabla de tallaje dice S = 2 días y la nota de al lado dice S ≈ 3 días. Se usó la tabla, porque es la que alimenta la fórmula de la columna F. Si el equipo confirma los 3 días, el total sube 22 días (hay 22 requisitos en S).</t>
         </is>
       </c>
     </row>
@@ -4239,11 +4243,11 @@
         </is>
       </c>
       <c r="M52" s="121">
-        <f>COUNTIF($J$5:$J$196,$L52)</f>
+        <f>COUNTIF($J$5:$J$203,$L52)</f>
         <v/>
       </c>
       <c r="N52" s="121">
-        <f>SUMIF($J$5:$J$196,$L52,$F$5:$F$196)</f>
+        <f>SUMIF($J$5:$J$203,$L52,$F$5:$F$203)</f>
         <v/>
       </c>
       <c r="O52" s="121">
@@ -4298,11 +4302,11 @@
         </is>
       </c>
       <c r="M53" s="121">
-        <f>COUNTIF($J$5:$J$196,$L53)</f>
+        <f>COUNTIF($J$5:$J$203,$L53)</f>
         <v/>
       </c>
       <c r="N53" s="121">
-        <f>SUMIF($J$5:$J$196,$L53,$F$5:$F$196)</f>
+        <f>SUMIF($J$5:$J$203,$L53,$F$5:$F$203)</f>
         <v/>
       </c>
       <c r="O53" s="121">
@@ -4370,11 +4374,11 @@
         </is>
       </c>
       <c r="M54" s="121">
-        <f>COUNTIF($J$5:$J$196,$L54)</f>
+        <f>COUNTIF($J$5:$J$203,$L54)</f>
         <v/>
       </c>
       <c r="N54" s="121">
-        <f>SUMIF($J$5:$J$196,$L54,$F$5:$F$196)</f>
+        <f>SUMIF($J$5:$J$203,$L54,$F$5:$F$203)</f>
         <v/>
       </c>
       <c r="O54" s="121">
@@ -10199,7 +10203,7 @@
       </c>
       <c r="D188" s="98" t="inlineStr">
         <is>
-          <t>Api orquestadora del Gestor de Coordinación: punto único de entrada por tipo de solicitud, con el mismo rol de orquestador que los otros dos gestores.</t>
+          <t>Api orquestadora por tipo de solicitud: punto único de entrada del gestor, con el mismo rol de orquestador que los otros dos.</t>
         </is>
       </c>
       <c r="E188" s="126" t="inlineStr">
@@ -10249,7 +10253,7 @@
       </c>
       <c r="D189" s="98" t="inlineStr">
         <is>
-          <t>Traza de la decisión de asignación: prestador elegido, criterio aplicado, candidatos descartados y peso de cada criterio en el momento de decidir.</t>
+          <t>Todo lo que el coordinador invoca queda en la traza con su agente y su versión; sus permisos se declaran en el plano de control y no en el gestor.</t>
         </is>
       </c>
       <c r="E189" s="126" t="inlineStr">
@@ -10299,7 +10303,7 @@
       </c>
       <c r="D190" s="98" t="inlineStr">
         <is>
-          <t>Publica al bus el evento de prestador asignado, con la llave de correlación del caso y del siniestro padre, para que la torre lo lea.</t>
+          <t>Publica al bus el evento de coordinación resuelta con proveedor asignado, si tenía convenio y si hubo rechazo del prestador, y con la llave de correlación del caso y del siniestro padre. Es lo que habilita medir tiempo hasta agenda y capacidad efectiva de la red.</t>
         </is>
       </c>
       <c r="E190" s="126" t="inlineStr">
@@ -10349,7 +10353,7 @@
       </c>
       <c r="D191" s="98" t="inlineStr">
         <is>
-          <t>Notifica al cliente el prestador asignado y cualquier cambio posterior de prestador.</t>
+          <t>Notifica tanto al asegurado el proveedor asignado como al prestador la autorización, y cualquier cambio posterior de proveedor.</t>
         </is>
       </c>
       <c r="E191" s="126" t="inlineStr">
@@ -10449,7 +10453,7 @@
       </c>
       <c r="D193" s="98" t="inlineStr">
         <is>
-          <t>Reglas de asignación versionadas con vigencia y autor, almacenadas fuera del código y expuestas como herramienta, no embebidas en lógica de aplicación.</t>
+          <t>Reglas del coordinador versionadas con vigencia y autor, almacenadas fuera del código y expuestas como herramienta, no embebidas en lógica de aplicación.</t>
         </is>
       </c>
       <c r="E193" s="126" t="inlineStr">
@@ -10499,7 +10503,7 @@
       </c>
       <c r="D194" s="98" t="inlineStr">
         <is>
-          <t>Pesos del ranking como configuración y no como código, administrados por la API de gestión y configuraciones del plano de control.</t>
+          <t>Pesos y parámetros del ordenamiento como configuración del plano de control, administrados por la API de gestión y no por despliegue de código.</t>
         </is>
       </c>
       <c r="E194" s="126" t="inlineStr">
@@ -10631,8 +10635,346 @@
         </is>
       </c>
     </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="98" t="inlineStr">
+        <is>
+          <t>RF-140</t>
+        </is>
+      </c>
+      <c r="B197" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C197" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D197" s="98" t="inlineStr">
+        <is>
+          <t>Modelo experto «Coordinador autorización»: microservicio del dominio, propiedad del negocio e invocado como herramienta, que resuelve la coordinación. En el nivel 1 decide con reglas duras y sin modelo.</t>
+        </is>
+      </c>
+      <c r="E197" s="126" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F197" s="98">
+        <f>IF($E197="",0,INDEX($M$5:$M$8,MATCH($E197,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G197" s="98">
+        <f>IF($F197=0,0,$F197/10)</f>
+        <v/>
+      </c>
+      <c r="H197" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C197,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I197" s="98" t="n"/>
+      <c r="J197" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K197" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="98" t="inlineStr">
+        <is>
+          <t>RF-141</t>
+        </is>
+      </c>
+      <c r="B198" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C198" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D198" s="98" t="inlineStr">
+        <is>
+          <t>Bandeja (Autorizado): estado propio del gestor cuando el proveedor queda aprobado. No existe en el core y hay que crearlo y exponerlo.</t>
+        </is>
+      </c>
+      <c r="E198" s="126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F198" s="98">
+        <f>IF($E198="",0,INDEX($M$5:$M$8,MATCH($E198,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G198" s="98">
+        <f>IF($F198=0,0,$F198/10)</f>
+        <v/>
+      </c>
+      <c r="H198" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C198,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I198" s="98" t="n"/>
+      <c r="J198" s="98" t="inlineStr">
+        <is>
+          <t>Determinística</t>
+        </is>
+      </c>
+      <c r="K198" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="98" t="inlineStr">
+        <is>
+          <t>RF-142</t>
+        </is>
+      </c>
+      <c r="B199" s="98" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="C199" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D199" s="98" t="inlineStr">
+        <is>
+          <t>El ajuste que la persona hace sobre el proveedor sugerido en la bandeja entra como etiqueta y alimenta el golden set del coordinador.</t>
+        </is>
+      </c>
+      <c r="E199" s="126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F199" s="98">
+        <f>IF($E199="",0,INDEX($M$5:$M$8,MATCH($E199,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G199" s="98">
+        <f>IF($F199=0,0,$F199/10)</f>
+        <v/>
+      </c>
+      <c r="H199" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C199,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I199" s="98" t="n"/>
+      <c r="J199" s="98" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K199" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="98" t="inlineStr">
+        <is>
+          <t>RT-059</t>
+        </is>
+      </c>
+      <c r="B200" s="98" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C200" s="98" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D200" s="98" t="inlineStr">
+        <is>
+          <t>Golden set del coordinador: versionado, con dueño explícito, balanceado entre casos que se resuelven y casos que escalan, y con compuerta de no regresión antes de promover una versión.</t>
+        </is>
+      </c>
+      <c r="E200" s="126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F200" s="98">
+        <f>IF($E200="",0,INDEX($M$5:$M$8,MATCH($E200,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G200" s="98">
+        <f>IF($F200=0,0,$F200/10)</f>
+        <v/>
+      </c>
+      <c r="H200" s="98">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C200,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I200" s="98" t="n"/>
+      <c r="J200" s="98" t="inlineStr">
+        <is>
+          <t>Habilitadora</t>
+        </is>
+      </c>
+      <c r="K200" s="127" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="106" t="inlineStr">
+        <is>
+          <t>RT-060</t>
+        </is>
+      </c>
+      <c r="B201" s="106" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C201" s="106" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D201" s="106" t="inlineStr">
+        <is>
+          <t>Re-coordinación: reasignar el proveedor cuando cambian las condiciones del caso.</t>
+        </is>
+      </c>
+      <c r="E201" s="107" t="n"/>
+      <c r="F201" s="106">
+        <f>IF($E201="",0,INDEX($M$5:$M$8,MATCH($E201,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G201" s="106">
+        <f>IF($F201=0,0,$F201/10)</f>
+        <v/>
+      </c>
+      <c r="H201" s="106">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C201,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I201" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No estimable. Las notas de diseño del equipo dicen que «la re-coordinación no es propia de torre de control, sino que debería ser capacidad de gestor de coordinación», pero no hay diseño, ni disparadores, ni alcance. Es una capacidad reconocida y sin dimensionar.</t>
+        </is>
+      </c>
+      <c r="J201" s="106" t="n"/>
+      <c r="K201" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="106" t="inlineStr">
+        <is>
+          <t>RT-061</t>
+        </is>
+      </c>
+      <c r="B202" s="106" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C202" s="106" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D202" s="106" t="inlineStr">
+        <is>
+          <t>Estados de respuesta del prestador sobre la autorización coordinada.</t>
+        </is>
+      </c>
+      <c r="E202" s="107" t="n"/>
+      <c r="F202" s="106">
+        <f>IF($E202="",0,INDEX($M$5:$M$8,MATCH($E202,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G202" s="106">
+        <f>IF($F202=0,0,$F202/10)</f>
+        <v/>
+      </c>
+      <c r="H202" s="106">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C202,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I202" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No estimable. El diseño base nombra «aprobación del prestador» y pide registrar «si hubo rechazo del prestador», y las notas de detalle abren recepción, aceptación, rechazo e imposibilidad de atención. Ninguno está diseñado como estado, y de ellos depende el evento que la torre consume.</t>
+        </is>
+      </c>
+      <c r="J202" s="106" t="n"/>
+      <c r="K202" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="30" customHeight="1">
+      <c r="A203" s="106" t="inlineStr">
+        <is>
+          <t>RT-062</t>
+        </is>
+      </c>
+      <c r="B203" s="106" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="C203" s="106" t="inlineStr">
+        <is>
+          <t>Gestor de Coordinación</t>
+        </is>
+      </c>
+      <c r="D203" s="106" t="inlineStr">
+        <is>
+          <t>Los otros dos modelos expertos previstos para este gestor.</t>
+        </is>
+      </c>
+      <c r="E203" s="107" t="n"/>
+      <c r="F203" s="106">
+        <f>IF($E203="",0,INDEX($M$5:$M$8,MATCH($E203,$L$5:$L$8,0)))</f>
+        <v/>
+      </c>
+      <c r="G203" s="106">
+        <f>IF($F203=0,0,$F203/10)</f>
+        <v/>
+      </c>
+      <c r="H203" s="106">
+        <f>IFERROR(INDEX($O$15:$O$29,MATCH($C203,$L$15:$L$29,0)),"🟨 validar")</f>
+        <v/>
+      </c>
+      <c r="I203" s="106" t="inlineStr">
+        <is>
+          <t>🟥 No estimable. El diseño base los dibuja como «dos modelos más, aún sin nombre». Nuestras propias notas advierten que un recuadro sin nombre es la primera pregunta de un sponsor. Sin nombre ni responsabilidad no hay nada que tallar.</t>
+        </is>
+      </c>
+      <c r="J203" s="106" t="n"/>
+      <c r="K203" s="125" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q196"/>
+  <autoFilter ref="A4:Q203"/>
   <mergeCells count="16">
     <mergeCell ref="M48:Q48"/>
     <mergeCell ref="M40:Q40"/>
@@ -10652,13 +10994,13 @@
     <mergeCell ref="L3:N3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="E5:E196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$L$5:$L$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Agéntica,Habilitadora,Determinística"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"v1,v2"</formula1>
     </dataValidation>
   </dataValidations>
